--- a/data/taxRefund.xlsx
+++ b/data/taxRefund.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="227">
   <si>
     <t>订单编号</t>
   </si>
@@ -33,6 +33,666 @@
   </si>
   <si>
     <t>报关单号</t>
+  </si>
+  <si>
+    <t>ATS25010</t>
+  </si>
+  <si>
+    <t>1426.5500</t>
+  </si>
+  <si>
+    <t>I-0032</t>
+  </si>
+  <si>
+    <t>氨基酸螯合镁</t>
+  </si>
+  <si>
+    <t>0.1150</t>
+  </si>
+  <si>
+    <t>20250721</t>
+  </si>
+  <si>
+    <t>222920250002635501</t>
+  </si>
+  <si>
+    <t>109522.1200</t>
+  </si>
+  <si>
+    <t>B-0012</t>
+  </si>
+  <si>
+    <t>辅酶Q10</t>
+  </si>
+  <si>
+    <t>20247.7900</t>
+  </si>
+  <si>
+    <t>A-0048</t>
+  </si>
+  <si>
+    <t>L-瓜氨酸</t>
+  </si>
+  <si>
+    <t>12516.8100</t>
+  </si>
+  <si>
+    <t>A-0050</t>
+  </si>
+  <si>
+    <t>L-瓜氨酸 DL-苹果酸</t>
+  </si>
+  <si>
+    <t>9939.8200</t>
+  </si>
+  <si>
+    <t>F-0102</t>
+  </si>
+  <si>
+    <t>甘油磷酰胆碱</t>
+  </si>
+  <si>
+    <t>5073.4500</t>
+  </si>
+  <si>
+    <t>A-0002</t>
+  </si>
+  <si>
+    <t>硫酸胍基丁胺</t>
+  </si>
+  <si>
+    <t>7880.5300</t>
+  </si>
+  <si>
+    <t>F-0077</t>
+  </si>
+  <si>
+    <t>辛弗林盐酸盐</t>
+  </si>
+  <si>
+    <t>48146.0100</t>
+  </si>
+  <si>
+    <t>B-0045</t>
+  </si>
+  <si>
+    <t>乙酰左旋肉碱盐酸盐</t>
+  </si>
+  <si>
+    <t>FTM2506047</t>
+  </si>
+  <si>
+    <t>15216.2100</t>
+  </si>
+  <si>
+    <t>H-0033</t>
+  </si>
+  <si>
+    <t>VE 软胶囊</t>
+  </si>
+  <si>
+    <t>20250829</t>
+  </si>
+  <si>
+    <t>010120250000417201</t>
+  </si>
+  <si>
+    <t>ATS25013</t>
+  </si>
+  <si>
+    <t>3681.4200</t>
+  </si>
+  <si>
+    <t>G-0022</t>
+  </si>
+  <si>
+    <t>明胶</t>
+  </si>
+  <si>
+    <t>20251002</t>
+  </si>
+  <si>
+    <t>222920250003666766</t>
+  </si>
+  <si>
+    <t>40035.4000</t>
+  </si>
+  <si>
+    <t>222920250003666904</t>
+  </si>
+  <si>
+    <t>782.3000</t>
+  </si>
+  <si>
+    <t>A-0038</t>
+  </si>
+  <si>
+    <t>L-精氨酸-α-酮戊二酸盐</t>
+  </si>
+  <si>
+    <t>FTM2509007</t>
+  </si>
+  <si>
+    <t>427.9700</t>
+  </si>
+  <si>
+    <t>C-0350</t>
+  </si>
+  <si>
+    <t>大黄提取物</t>
+  </si>
+  <si>
+    <t>20251001</t>
+  </si>
+  <si>
+    <t>222920250003672300</t>
+  </si>
+  <si>
+    <t>FTM2506050</t>
+  </si>
+  <si>
+    <t>5637.1700</t>
+  </si>
+  <si>
+    <t>C-0266</t>
+  </si>
+  <si>
+    <t>水飞蓟提取物</t>
+  </si>
+  <si>
+    <t>20250802</t>
+  </si>
+  <si>
+    <t>223120250003042327</t>
+  </si>
+  <si>
+    <t>SMK25001</t>
+  </si>
+  <si>
+    <t>67185.8400</t>
+  </si>
+  <si>
+    <t>B-0038</t>
+  </si>
+  <si>
+    <t>左旋肉碱</t>
+  </si>
+  <si>
+    <t>20250908</t>
+  </si>
+  <si>
+    <t>223120250003655802</t>
+  </si>
+  <si>
+    <t>FTM2508024</t>
+  </si>
+  <si>
+    <t>2761.0600</t>
+  </si>
+  <si>
+    <t>C-0087</t>
+  </si>
+  <si>
+    <t>姜黄素</t>
+  </si>
+  <si>
+    <t>20250905</t>
+  </si>
+  <si>
+    <t>223320250001481533</t>
+  </si>
+  <si>
+    <t>FTM2509017</t>
+  </si>
+  <si>
+    <t>6384.9600</t>
+  </si>
+  <si>
+    <t>H-0019</t>
+  </si>
+  <si>
+    <t>牛至油软胶囊</t>
+  </si>
+  <si>
+    <t>20250924</t>
+  </si>
+  <si>
+    <t>223320250001614356</t>
+  </si>
+  <si>
+    <t>ATS25011</t>
+  </si>
+  <si>
+    <t>299.1100</t>
+  </si>
+  <si>
+    <t>I-0034</t>
+  </si>
+  <si>
+    <t>天门冬氨酸镁</t>
+  </si>
+  <si>
+    <t>20250816</t>
+  </si>
+  <si>
+    <t>422720250000878606</t>
+  </si>
+  <si>
+    <t>FTM2508010</t>
+  </si>
+  <si>
+    <t>3853.9800</t>
+  </si>
+  <si>
+    <t>B-0014</t>
+  </si>
+  <si>
+    <t>肌醇</t>
+  </si>
+  <si>
+    <t>20250902</t>
+  </si>
+  <si>
+    <t>422720250000932733</t>
+  </si>
+  <si>
+    <t>FTM2509025 &amp; FTM2509032</t>
+  </si>
+  <si>
+    <t>1265.4900</t>
+  </si>
+  <si>
+    <t>C-0163</t>
+  </si>
+  <si>
+    <t>石杉碱甲1%</t>
+  </si>
+  <si>
+    <t>20251007</t>
+  </si>
+  <si>
+    <t>010120250000494035</t>
+  </si>
+  <si>
+    <t>FTM2508032</t>
+  </si>
+  <si>
+    <t>103539.8200</t>
+  </si>
+  <si>
+    <t>E-0004</t>
+  </si>
+  <si>
+    <t>胶原蛋白肽</t>
+  </si>
+  <si>
+    <t>20250919</t>
+  </si>
+  <si>
+    <t>222920250003478273</t>
+  </si>
+  <si>
+    <t>1495.5700</t>
+  </si>
+  <si>
+    <t>A-0088</t>
+  </si>
+  <si>
+    <t>甘氨酸镁</t>
+  </si>
+  <si>
+    <t>21398.2300</t>
+  </si>
+  <si>
+    <t>24734.5100</t>
+  </si>
+  <si>
+    <t>FTM2508012&amp;FTM2508014&amp;FTM2508027</t>
+  </si>
+  <si>
+    <t>8724.1300</t>
+  </si>
+  <si>
+    <t>H-0013</t>
+  </si>
+  <si>
+    <t>芦荟软胶囊</t>
+  </si>
+  <si>
+    <t>223120250004036295</t>
+  </si>
+  <si>
+    <t>14926.1900</t>
+  </si>
+  <si>
+    <t>H-0012</t>
+  </si>
+  <si>
+    <t>维生素 D3 &amp; VK2 软胶囊</t>
+  </si>
+  <si>
+    <t>10966.9700</t>
+  </si>
+  <si>
+    <t>K-0023</t>
+  </si>
+  <si>
+    <t>OMEGA 3 软胶囊</t>
+  </si>
+  <si>
+    <t>3189.0300</t>
+  </si>
+  <si>
+    <t>H-0011</t>
+  </si>
+  <si>
+    <t>亚麻籽油软胶囊</t>
+  </si>
+  <si>
+    <t>7665.0100</t>
+  </si>
+  <si>
+    <t>H-0010</t>
+  </si>
+  <si>
+    <t>VE软胶囊</t>
+  </si>
+  <si>
+    <t>FTM2508014-1</t>
+  </si>
+  <si>
+    <t>14046.9000</t>
+  </si>
+  <si>
+    <t>223120250004036309</t>
+  </si>
+  <si>
+    <t>FTM2509021</t>
+  </si>
+  <si>
+    <t>20250926</t>
+  </si>
+  <si>
+    <t>223320250001628411</t>
+  </si>
+  <si>
+    <t>FTM2509006</t>
+  </si>
+  <si>
+    <t>224.3400</t>
+  </si>
+  <si>
+    <t>C-0349</t>
+  </si>
+  <si>
+    <t>猴头菇提取物</t>
+  </si>
+  <si>
+    <t>20250916</t>
+  </si>
+  <si>
+    <t>224420250014056507</t>
+  </si>
+  <si>
+    <t>FTM2510004</t>
+  </si>
+  <si>
+    <t>241.5900</t>
+  </si>
+  <si>
+    <t>I-0003</t>
+  </si>
+  <si>
+    <t>复合矿物质-Min</t>
+  </si>
+  <si>
+    <t>20251020</t>
+  </si>
+  <si>
+    <t>224420250015880546</t>
+  </si>
+  <si>
+    <t>FTM2510018</t>
+  </si>
+  <si>
+    <t>143.8000</t>
+  </si>
+  <si>
+    <t>A-0016</t>
+  </si>
+  <si>
+    <t>肌酸硝酸盐</t>
+  </si>
+  <si>
+    <t>20251021</t>
+  </si>
+  <si>
+    <t>224420250015973455</t>
+  </si>
+  <si>
+    <t>ATS25011-1</t>
+  </si>
+  <si>
+    <t>647.1200</t>
+  </si>
+  <si>
+    <t>I-0044</t>
+  </si>
+  <si>
+    <t>氨基酸螯合锌</t>
+  </si>
+  <si>
+    <t>422720250000878594</t>
+  </si>
+  <si>
+    <t>FTM2509027</t>
+  </si>
+  <si>
+    <t>2139.5500</t>
+  </si>
+  <si>
+    <t>H-0014</t>
+  </si>
+  <si>
+    <t>维生素D3软胶囊</t>
+  </si>
+  <si>
+    <t>20251025</t>
+  </si>
+  <si>
+    <t>425820250001341283</t>
+  </si>
+  <si>
+    <t>SMK25002</t>
+  </si>
+  <si>
+    <t>10986.7300</t>
+  </si>
+  <si>
+    <t>A-0082</t>
+  </si>
+  <si>
+    <t>L-茶氨酸</t>
+  </si>
+  <si>
+    <t>425820250001341979</t>
+  </si>
+  <si>
+    <t>FTM2505023</t>
+  </si>
+  <si>
+    <t>1610.6200</t>
+  </si>
+  <si>
+    <t>J-0013</t>
+  </si>
+  <si>
+    <t>彩盒</t>
+  </si>
+  <si>
+    <t>20251018</t>
+  </si>
+  <si>
+    <t>534520250450746974</t>
+  </si>
+  <si>
+    <t>2329.6500</t>
+  </si>
+  <si>
+    <t>C-0119</t>
+  </si>
+  <si>
+    <t>藤黄果提取物</t>
+  </si>
+  <si>
+    <t>FTM2510027</t>
+  </si>
+  <si>
+    <t>33702.2100</t>
+  </si>
+  <si>
+    <t>A-0014</t>
+  </si>
+  <si>
+    <t>一水肌酸</t>
+  </si>
+  <si>
+    <t>20251106</t>
+  </si>
+  <si>
+    <t>020220250001182607</t>
+  </si>
+  <si>
+    <t>ATS25014</t>
+  </si>
+  <si>
+    <t>897.3400</t>
+  </si>
+  <si>
+    <t>A-0079</t>
+  </si>
+  <si>
+    <t>L-苯丙氨酸</t>
+  </si>
+  <si>
+    <t>20251122</t>
+  </si>
+  <si>
+    <t>222920250004383560</t>
+  </si>
+  <si>
+    <t>11044.2500</t>
+  </si>
+  <si>
+    <t>A-0074</t>
+  </si>
+  <si>
+    <t>L-正缬氨酸</t>
+  </si>
+  <si>
+    <t>1668.1400</t>
+  </si>
+  <si>
+    <t>222920250004383564</t>
+  </si>
+  <si>
+    <t>4969.9100</t>
+  </si>
+  <si>
+    <t>5464.6000</t>
+  </si>
+  <si>
+    <t>G-0016</t>
+  </si>
+  <si>
+    <t>三氯蔗糖</t>
+  </si>
+  <si>
+    <t>2013.2700</t>
+  </si>
+  <si>
+    <t>A-0101</t>
+  </si>
+  <si>
+    <t>牛磺酸</t>
+  </si>
+  <si>
+    <t>506.2000</t>
+  </si>
+  <si>
+    <t>20221.3300</t>
+  </si>
+  <si>
+    <t>FTM2509018</t>
+  </si>
+  <si>
+    <t>12603.8100</t>
+  </si>
+  <si>
+    <t>H-0032</t>
+  </si>
+  <si>
+    <t>复合鱼油软胶囊</t>
+  </si>
+  <si>
+    <t>20251105</t>
+  </si>
+  <si>
+    <t>223120250004446425</t>
+  </si>
+  <si>
+    <t>FTM2509016</t>
+  </si>
+  <si>
+    <t>655.7500</t>
+  </si>
+  <si>
+    <t>C-0069</t>
+  </si>
+  <si>
+    <t>枳实提取物</t>
+  </si>
+  <si>
+    <t>20250922</t>
+  </si>
+  <si>
+    <t>224420250014460242</t>
+  </si>
+  <si>
+    <t>FTM2511002</t>
+  </si>
+  <si>
+    <t>2588.5000</t>
+  </si>
+  <si>
+    <t>F-0017</t>
+  </si>
+  <si>
+    <t>还原型谷胱甘肽</t>
+  </si>
+  <si>
+    <t>20251113</t>
+  </si>
+  <si>
+    <t>224420250017193761</t>
+  </si>
+  <si>
+    <t>5867.2600</t>
+  </si>
+  <si>
+    <t>C-0319</t>
+  </si>
+  <si>
+    <t>支链氨基酸</t>
+  </si>
+  <si>
+    <t>4256.6400</t>
+  </si>
+  <si>
+    <t>F-0109</t>
+  </si>
+  <si>
+    <t>二甲氨基乙醇酒石酸氢盐</t>
   </si>
 </sst>
 </file>
@@ -77,7 +737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -103,6 +763,1248 @@
         <v>6</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="E15" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="C16" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="E16" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="E17" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="E18" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="E19" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="E22" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="E23" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="E24" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="E25" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="C26" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="E26" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="C27" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="E27" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="C28" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="E28" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="E29" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="C30" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="E30" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>128</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>129</v>
+      </c>
+      <c r="C31" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="E31" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="E32" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>132</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="E33" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>140</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="E34" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F34" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="E35" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="G35" t="s" s="0">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>152</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>153</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="E36" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>158</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="E37" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F37" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="G37" t="s" s="0">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="D38" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="E38" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F38" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="G38" t="s" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>168</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>169</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="D39" t="s" s="0">
+        <v>171</v>
+      </c>
+      <c r="E39" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F39" t="s" s="0">
+        <v>172</v>
+      </c>
+      <c r="G39" t="s" s="0">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="D40" t="s" s="0">
+        <v>176</v>
+      </c>
+      <c r="E40" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F40" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="G40" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="D41" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="E41" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F41" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="G41" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="D42" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="E42" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F42" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="G42" t="s" s="0">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>184</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="D43" t="s" s="0">
+        <v>186</v>
+      </c>
+      <c r="E43" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F43" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="G43" t="s" s="0">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>189</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>190</v>
+      </c>
+      <c r="D44" t="s" s="0">
+        <v>191</v>
+      </c>
+      <c r="E44" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F44" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="G44" t="s" s="0">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>192</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="D45" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="E45" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F45" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="G45" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D46" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="E46" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F46" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="G46" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>196</v>
+      </c>
+      <c r="D47" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="E47" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F47" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="G47" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>198</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="D48" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="E48" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F48" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="G48" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>148</v>
+      </c>
+      <c r="D49" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="E49" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F49" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="G49" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="D50" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="E50" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F50" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="G50" t="s" s="0">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="D51" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="E51" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F51" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="G51" t="s" s="0">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="D52" t="s" s="0">
+        <v>212</v>
+      </c>
+      <c r="E52" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F52" t="s" s="0">
+        <v>213</v>
+      </c>
+      <c r="G52" t="s" s="0">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>215</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>216</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>217</v>
+      </c>
+      <c r="D53" t="s" s="0">
+        <v>218</v>
+      </c>
+      <c r="E53" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F53" t="s" s="0">
+        <v>219</v>
+      </c>
+      <c r="G53" t="s" s="0">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>221</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="D54" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="E54" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F54" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="G54" t="s" s="0">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>225</v>
+      </c>
+      <c r="D55" t="s" s="0">
+        <v>226</v>
+      </c>
+      <c r="E55" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="F55" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="G55" t="s" s="0">
+        <v>167</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
